--- a/www/download/IND.gdp.s.mv.rpA2.xlsx
+++ b/www/download/IND.gdp.s.mv.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17789.693</t>
+          <t>17789692754.5893</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18015.713</t>
+          <t>18015713019.4305</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18409.98</t>
+          <t>18409979553.7644</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18928.414</t>
+          <t>18928414496.5305</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19427.729</t>
+          <t>19427728760.4546</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20080.911</t>
+          <t>20080911052.6804</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20357.827</t>
+          <t>20357827154.5393</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21003.355</t>
+          <t>21003355283.7192</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>21697.285</t>
+          <t>21697284961.7</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21899.607</t>
+          <t>21899606553.9041</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22688.726</t>
+          <t>22688725702.1586</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>23407.922</t>
+          <t>23407921964.4599</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>24070.066</t>
+          <t>24070066114.6991</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>25946.739</t>
+          <t>25946739182.1103</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>27369.435</t>
+          <t>27369434935.5338</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9022.606</t>
+          <t>9022606045.26206</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9115.252</t>
+          <t>9115252134.85817</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9269.28</t>
+          <t>9269279769.70427</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9368.341</t>
+          <t>9368340678.44368</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9522.091</t>
+          <t>9522091449.96329</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9634.249</t>
+          <t>9634248536.9922</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9832.995</t>
+          <t>9832994936.39542</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9890.157</t>
+          <t>9890156890.99355</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>9770.009</t>
+          <t>9770009313.48565</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10299.575</t>
+          <t>10299574989.1529</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10124.553</t>
+          <t>10124552615.7472</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10080.409</t>
+          <t>10080409222.265</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>10132.311</t>
+          <t>10132310943.9466</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>10354.337</t>
+          <t>10354336955.6329</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>9893.189</t>
+          <t>9893188573.52786</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6320.031</t>
+          <t>6320031462.34318</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6341.727</t>
+          <t>6341727085.4783</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6438.945</t>
+          <t>6438945495.18405</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6534.907</t>
+          <t>6534907301.43032</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6624.338</t>
+          <t>6624338155.01936</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6854.747</t>
+          <t>6854747498.66849</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6958.035</t>
+          <t>6958035095.64287</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6903.131</t>
+          <t>6903131078.49035</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6900.226</t>
+          <t>6900225791.5892</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7049.658</t>
+          <t>7049658274.60795</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>7086.909</t>
+          <t>7086909210.74418</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7196.366</t>
+          <t>7196366486.35599</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>7332.79</t>
+          <t>7332789538.14424</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>7720.728</t>
+          <t>7720727852.61228</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>7618.891</t>
+          <t>7618890997.6191</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6689.861</t>
+          <t>6689861470.03589</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6786.864</t>
+          <t>6786864165.83794</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6455.995</t>
+          <t>6455994658.17914</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5934.017</t>
+          <t>5934016893.05601</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5681.779</t>
+          <t>5681779001.31758</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5374.793</t>
+          <t>5374792786.25466</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5187.625</t>
+          <t>5187624594.50755</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5141.831</t>
+          <t>5141830720.27135</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5324.817</t>
+          <t>5324817059.55235</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5663.816</t>
+          <t>5663816148.80318</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5805.855</t>
+          <t>5805854892.35813</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6006.339</t>
+          <t>6006339428.20481</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>6195.95</t>
+          <t>6195950448.10717</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6261.33</t>
+          <t>6261329713.29465</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>6216.608</t>
+          <t>6216608447.23869</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>140510.637</t>
+          <t>140510637261.15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>138850.013</t>
+          <t>138850012718.052</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>143361.453</t>
+          <t>143361453076.684</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>143453.964</t>
+          <t>143453963578.339</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>151058.151</t>
+          <t>151058150809.165</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>156452.926</t>
+          <t>156452926091.656</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>158599.629</t>
+          <t>158599628924.117</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>164678.276</t>
+          <t>164678276104.962</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>169666.982</t>
+          <t>169666981617.229</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>181521.407</t>
+          <t>181521406903.966</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>188020.203</t>
+          <t>188020202639.084</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>195362.116</t>
+          <t>195362115713.39</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>206111.388</t>
+          <t>206111387869.917</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>217687.168</t>
+          <t>217687167609.526</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>220018.053</t>
+          <t>220018053499.365</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>33254.688</t>
+          <t>33254688392.1349</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>33803.966</t>
+          <t>33803965620.9691</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34560.2</t>
+          <t>34560200350.4792</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>34940.534</t>
+          <t>34940534397.1928</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>35410.618</t>
+          <t>35410618444.7986</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>36447.634</t>
+          <t>36447634006.3778</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>36163.92</t>
+          <t>36163920153.2055</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36478.138</t>
+          <t>36478137797.8286</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>37023.154</t>
+          <t>37023153586.8513</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>38065.723</t>
+          <t>38065723252.6162</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>38656.008</t>
+          <t>38656008037.4245</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>39422.102</t>
+          <t>39422101863.7109</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>40211.395</t>
+          <t>40211395303.3007</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>40470.981</t>
+          <t>40470981408.468</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>39656.294</t>
+          <t>39656294308.6401</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1284365.182</t>
+          <t>1284365181897.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1308696.195</t>
+          <t>1308696194938.17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1327857.058</t>
+          <t>1327857058135.14</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1330314.961</t>
+          <t>1330314961448.86</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1353243.144</t>
+          <t>1353243144170.34</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1374320.852</t>
+          <t>1374320852171.52</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1406875.094</t>
+          <t>1406875094434.02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1443981.949</t>
+          <t>1443981948939.2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1484366.622</t>
+          <t>1484366622424.51</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1521157.989</t>
+          <t>1521157989032.58</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1561400.042</t>
+          <t>1561400041690.57</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1650258.277</t>
+          <t>1650258277330.52</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1691169.058</t>
+          <t>1691169057604.6</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1773178.187</t>
+          <t>1773178187230.62</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1793196.863</t>
+          <t>1793196862783.44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>727.779</t>
+          <t>727778959.588986</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>724.189</t>
+          <t>724188516.296073</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>707.664</t>
+          <t>707663883.648339</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>688.374</t>
+          <t>688374166.163068</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>688.949</t>
+          <t>688949270.733544</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>708.308</t>
+          <t>708308401.412657</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>729.231</t>
+          <t>729231376.62469</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>737.966</t>
+          <t>737965903.476912</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>760.854</t>
+          <t>760854284.325791</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>760.286</t>
+          <t>760285871.186763</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>770.475</t>
+          <t>770474506.204805</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>789.104</t>
+          <t>789103547.869181</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>847.728</t>
+          <t>847727621.472844</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>847.36</t>
+          <t>847360259.453504</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>848.057</t>
+          <t>848057350.630386</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17246.464</t>
+          <t>17246463630.7287</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17461.797</t>
+          <t>17461797280.2305</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17363.807</t>
+          <t>17363807375.4458</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17057.704</t>
+          <t>17057703608.8577</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>16522.028</t>
+          <t>16522027902.1114</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>16391.849</t>
+          <t>16391848661.1106</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15836.89</t>
+          <t>15836889793.0014</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15686.148</t>
+          <t>15686147993.6791</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>15412.527</t>
+          <t>15412526758.3581</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>15643.09</t>
+          <t>15643089568.4064</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>16022.943</t>
+          <t>16022943443.0659</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>16315.489</t>
+          <t>16315488778.5009</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>16516.63</t>
+          <t>16516629538.338</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>16989.993</t>
+          <t>16989993191.3286</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>16324.947</t>
+          <t>16324947057.4808</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>94629.744</t>
+          <t>94629743593.2316</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>91310.368</t>
+          <t>91310368223.3416</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>89837.832</t>
+          <t>89837832034.3608</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>92857.402</t>
+          <t>92857401544.4347</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>91738.565</t>
+          <t>91738564898.06</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>90903.901</t>
+          <t>90903901156.5486</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>89944.246</t>
+          <t>89944245858.607</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>88909.474</t>
+          <t>88909473690.2631</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>90076.831</t>
+          <t>90076831200.654</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>91725.918</t>
+          <t>91725918206.0993</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>89140.453</t>
+          <t>89140453217.7088</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>88194.152</t>
+          <t>88194151953.974</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>89441.463</t>
+          <t>89441462881.9583</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>90284.882</t>
+          <t>90284881810.2775</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>89465.148</t>
+          <t>89465147914.2947</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6863.723</t>
+          <t>6863722992.71416</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6881.346</t>
+          <t>6881345769.75569</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7111.027</t>
+          <t>7111026882.95835</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7344.62</t>
+          <t>7344619737.80094</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7487.524</t>
+          <t>7487523621.54814</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7587.229</t>
+          <t>7587229105.83669</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7671.847</t>
+          <t>7671847410.54679</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7711.192</t>
+          <t>7711191631.86663</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7709.923</t>
+          <t>7709923308.5295</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7714.215</t>
+          <t>7714214803.74415</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7866.785</t>
+          <t>7866785091.69985</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>8047.714</t>
+          <t>8047713779.47736</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>7654.908</t>
+          <t>7654908397.42842</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>8012.063</t>
+          <t>8012063472.75087</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>7831.565</t>
+          <t>7831564979.52882</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>28033.615</t>
+          <t>28033615031.9551</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29558.969</t>
+          <t>29558968882.5143</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31022.863</t>
+          <t>31022863274.8839</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>32950.029</t>
+          <t>32950028848.3571</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>34833.92</t>
+          <t>34833920199.4542</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>37553.091</t>
+          <t>37553090970.8254</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>38947.026</t>
+          <t>38947025705.2194</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>40589.006</t>
+          <t>40589005674.9376</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>41858.376</t>
+          <t>41858375624.9438</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>43292.056</t>
+          <t>43292055504.1093</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45700.54</t>
+          <t>45700540166.206</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>47512.685</t>
+          <t>47512684663.0169</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>48560.531</t>
+          <t>48560530591.3084</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>47705.093</t>
+          <t>47705093111.3475</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>44631.88</t>
+          <t>44631880250.7411</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2658.033</t>
+          <t>2658032653.89877</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2555.859</t>
+          <t>2555858945.57419</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2496.864</t>
+          <t>2496863999.12794</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2378.424</t>
+          <t>2378423699.84485</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2186.019</t>
+          <t>2186018983.32026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2140.494</t>
+          <t>2140494307.13677</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2212.18</t>
+          <t>2212179601.74322</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2209.661</t>
+          <t>2209660819.35729</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2286.632</t>
+          <t>2286632173.66386</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2396.981</t>
+          <t>2396980784.70086</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2415.506</t>
+          <t>2415506323.31016</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2552.204</t>
+          <t>2552204160.37232</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2592.553</t>
+          <t>2592552935.50933</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2538.348</t>
+          <t>2538348325.09053</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2209.743</t>
+          <t>2209743264.3613</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6880.147</t>
+          <t>6880146514.53004</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6983.286</t>
+          <t>6983286382.10359</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7249.026</t>
+          <t>7249026315.02325</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7341.177</t>
+          <t>7341177475.75869</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7517.938</t>
+          <t>7517937733.54533</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7544.224</t>
+          <t>7544224213.92795</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7632.936</t>
+          <t>7632935715.81236</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7692.598</t>
+          <t>7692598346.02183</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7625.482</t>
+          <t>7625482157.25882</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7787.606</t>
+          <t>7787606429.7366</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7870.687</t>
+          <t>7870687128.35334</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8019.112</t>
+          <t>8019112370.50843</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>8212.567</t>
+          <t>8212567300.39863</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>8320.849</t>
+          <t>8320848793.9919</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>8132.551</t>
+          <t>8132550579.83207</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>48609.007</t>
+          <t>48609006686.5923</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49303.913</t>
+          <t>49303913165.3741</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>49672.424</t>
+          <t>49672424158.9199</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>50281.432</t>
+          <t>50281432226.0801</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>51313.084</t>
+          <t>51313084020.1982</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>51016.92</t>
+          <t>51016919946.6087</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>51655.61</t>
+          <t>51655609567.7032</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>50959.593</t>
+          <t>50959592607.318</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>50774.325</t>
+          <t>50774325231.4955</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>51816.794</t>
+          <t>51816793556.6777</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>52550.154</t>
+          <t>52550154214.4444</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>53094.514</t>
+          <t>53094514283.1918</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>55645.164</t>
+          <t>55645163716.4073</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>57073.765</t>
+          <t>57073764862.5279</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>56202.365</t>
+          <t>56202365058.5393</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>61371.537</t>
+          <t>61371537318.0095</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>61787.906</t>
+          <t>61787905982.2907</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>64481.889</t>
+          <t>64481889155.867</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>66095.431</t>
+          <t>66095431324.9535</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>67186.442</t>
+          <t>67186442377.2982</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>68195.481</t>
+          <t>68195480928.4519</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>68632.624</t>
+          <t>68632624429.4507</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>69676.434</t>
+          <t>69676434085.4315</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>69584.651</t>
+          <t>69584650707.1666</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>69692.778</t>
+          <t>69692778047.3355</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>70674.784</t>
+          <t>70674783924.364</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>71501.702</t>
+          <t>71501702301.598</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>72121.562</t>
+          <t>72121561669.3942</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>71644.402</t>
+          <t>71644401993.8083</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>71882.54</t>
+          <t>71882540094.0482</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9261.626</t>
+          <t>9261626464.21733</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9263.147</t>
+          <t>9263147473.9873</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9120.758</t>
+          <t>9120757591.50051</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>9613.144</t>
+          <t>9613143753.97562</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9885.076</t>
+          <t>9885076079.80919</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>9935.398</t>
+          <t>9935398095.52101</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9895.203</t>
+          <t>9895203485.67614</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9982.645</t>
+          <t>9982645261.82571</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>9978.656</t>
+          <t>9978656039.19299</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>10577.004</t>
+          <t>10577004211.5618</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10478.967</t>
+          <t>10478966820.4792</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>11256.006</t>
+          <t>11256006219.3967</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>11454.472</t>
+          <t>11454472053.4127</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>11324.502</t>
+          <t>11324502202.8121</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>11491.389</t>
+          <t>11491388934.4534</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14025.416</t>
+          <t>14025415945.6601</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13924.036</t>
+          <t>13924036492.8237</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13892.732</t>
+          <t>13892732153.1488</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14189.983</t>
+          <t>14189982549.8933</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14856.861</t>
+          <t>14856861427.17</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14611.374</t>
+          <t>14611373737.2909</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14198.442</t>
+          <t>14198441779.2012</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>14342.248</t>
+          <t>14342248468.5026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>14301.702</t>
+          <t>14301701526.121</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>14435.83</t>
+          <t>14435830494.4513</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>14096.701</t>
+          <t>14096701211.5942</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>14271.698</t>
+          <t>14271697858.8496</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>14194.558</t>
+          <t>14194557721.8169</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>13580.238</t>
+          <t>13580237581.8277</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>13776.557</t>
+          <t>13776556776.0653</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>118548.023</t>
+          <t>118548022859.917</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>122305.491</t>
+          <t>122305491029.377</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>120817.284</t>
+          <t>120817284265.849</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>125669.873</t>
+          <t>125669872630.795</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>136820.634</t>
+          <t>136820634477.831</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>147060.511</t>
+          <t>147060511350.226</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>148242.356</t>
+          <t>148242356229.072</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>154957.671</t>
+          <t>154957671049.301</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>159536.537</t>
+          <t>159536536506.834</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>164008.211</t>
+          <t>164008211072.08</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>147072.009</t>
+          <t>147072009427.296</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>139455.111</t>
+          <t>139455111274.189</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>143565.102</t>
+          <t>143565101620.111</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>144380.499</t>
+          <t>144380499177.016</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>147661.354</t>
+          <t>147661354362.392</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1078913.368</t>
+          <t>1078913367597.13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1125626.688</t>
+          <t>1125626688159.55</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1147411.902</t>
+          <t>1147411902372.16</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1164967.15</t>
+          <t>1164967149606.02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1162078.298</t>
+          <t>1162078297589.72</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1237074.426</t>
+          <t>1237074425812.64</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1308854.157</t>
+          <t>1308854157442.03</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1311640.117</t>
+          <t>1311640116950.66</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1399899.956</t>
+          <t>1399899955842.74</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1455738.203</t>
+          <t>1455738203145.66</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1499258.714</t>
+          <t>1499258714262.8</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1511648.947</t>
+          <t>1511648946832.61</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1478942.161</t>
+          <t>1478942161277.23</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1490588.477</t>
+          <t>1490588476553.69</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1498779.698</t>
+          <t>1498779698103.75</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3895.103</t>
+          <t>3895102823.13994</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4160.955</t>
+          <t>4160955010.04332</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4298.79</t>
+          <t>4298790121.57756</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4574.59</t>
+          <t>4574589705.4159</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4878.113</t>
+          <t>4878113494.12028</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5093.476</t>
+          <t>5093476465.99016</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5259.257</t>
+          <t>5259257081.2274</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>5425.613</t>
+          <t>5425613161.41313</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5620.591</t>
+          <t>5620591269.51637</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5897.25</t>
+          <t>5897250120.46106</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>6261.547</t>
+          <t>6261546758.54725</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6679.938</t>
+          <t>6679938132.74748</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>6927.776</t>
+          <t>6927775924.06425</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>7243.132</t>
+          <t>7243132359.43455</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>6930.963</t>
+          <t>6930962634.08325</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>39151.876</t>
+          <t>39151875718.7615</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>39988.59</t>
+          <t>39988589784.0459</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>40959.019</t>
+          <t>40959019369.3306</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>42638.172</t>
+          <t>42638171975.2026</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>43535.273</t>
+          <t>43535272876.1799</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>43726.593</t>
+          <t>43726593244.4663</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>43258.79</t>
+          <t>43258789548.0469</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>43735.644</t>
+          <t>43735643798.9918</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>44785.2</t>
+          <t>44785199526.7311</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>45433.93</t>
+          <t>45433930135.9473</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>46812.032</t>
+          <t>46812032066.1867</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>48266.861</t>
+          <t>48266861001.9457</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>49314.445</t>
+          <t>49314445312.3592</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>50422.893</t>
+          <t>50422893450.2674</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>48549.407</t>
+          <t>48549407117.7642</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>190758.977</t>
+          <t>190758977119.138</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>192679.472</t>
+          <t>192679471799.875</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>193425.837</t>
+          <t>193425836607.363</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>188628.7</t>
+          <t>188628700287.614</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>186004.813</t>
+          <t>186004813094.526</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>187362.768</t>
+          <t>187362767818.476</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>186611.471</t>
+          <t>186611470588.726</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>182923.854</t>
+          <t>182923853872.446</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>184383.598</t>
+          <t>184383598099.934</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>184725</t>
+          <t>184725000370.948</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>182234.55</t>
+          <t>182234550312.68</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>183318.048</t>
+          <t>183318047859.215</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>183649.141</t>
+          <t>183649140927.156</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>177499.233</t>
+          <t>177499233185.077</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>164343.253</t>
+          <t>164343253375.303</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>94721.364</t>
+          <t>94721363734.9359</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>94600.555</t>
+          <t>94600554793.3239</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>95448.07</t>
+          <t>95448070306.6179</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>91753.189</t>
+          <t>91753188950.8484</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>94515.36</t>
+          <t>94515359997.4082</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>99544.036</t>
+          <t>99544035554.4032</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100674.823</t>
+          <t>100674822827.191</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>103357.556</t>
+          <t>103357556499.1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>105770.589</t>
+          <t>105770588734.623</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>111208.513</t>
+          <t>111208513446.681</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>107140.216</t>
+          <t>107140216400.811</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>107355.731</t>
+          <t>107355730848.91</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>104899.392</t>
+          <t>104899392213.438</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>105539.459</t>
+          <t>105539459336.092</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>105221.664</t>
+          <t>105221663771.698</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5515.267</t>
+          <t>5515267400.99386</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5503.216</t>
+          <t>5503216273.3625</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5328.017</t>
+          <t>5328016579.10688</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>5458.676</t>
+          <t>5458675733.13771</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5105.055</t>
+          <t>5105054920.23628</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5327.967</t>
+          <t>5327966812.74797</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5098.418</t>
+          <t>5098417905.80103</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5072.288</t>
+          <t>5072288064.30586</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5226.603</t>
+          <t>5226603064.40357</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5268.226</t>
+          <t>5268225776.78454</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>5656.093</t>
+          <t>5656092634.79602</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5582.956</t>
+          <t>5582956421.28812</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>5929.463</t>
+          <t>5929463493.84259</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>5994.761</t>
+          <t>5994761082.88008</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5526.222</t>
+          <t>5526221719.02264</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>387.982</t>
+          <t>387982467.058771</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>392.322</t>
+          <t>392321560.25952</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>409.448</t>
+          <t>409448137.801256</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>428.284</t>
+          <t>428283891.056645</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>436.312</t>
+          <t>436311988.408397</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>461.91</t>
+          <t>461909607.09828</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>476.748</t>
+          <t>476747950.456034</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>494.454</t>
+          <t>494454087.743846</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>477.5</t>
+          <t>477500211.815212</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>558.356</t>
+          <t>558355739.516445</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>578.182</t>
+          <t>578182453.090166</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>574.695</t>
+          <t>574694636.279294</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>601.362</t>
+          <t>601361862.420274</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>644.973</t>
+          <t>644972516.307062</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>743.527</t>
+          <t>743526934.970109</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2979.955</t>
+          <t>2979955282.1514</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2939.442</t>
+          <t>2939441924.62795</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2934.065</t>
+          <t>2934064832.47225</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2824.276</t>
+          <t>2824275515.96955</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2657.376</t>
+          <t>2657376042.63289</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2470.383</t>
+          <t>2470383459.65591</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2406.407</t>
+          <t>2406407461.47794</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2354.991</t>
+          <t>2354990720.0215</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2386.656</t>
+          <t>2386656176.52722</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2444.217</t>
+          <t>2444216883.62993</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2425.131</t>
+          <t>2425131476.29214</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2544.979</t>
+          <t>2544978690.85961</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2603.23</t>
+          <t>2603229877.68746</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2590.181</t>
+          <t>2590180980.37258</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1995.036</t>
+          <t>1995035981.24308</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>90709.211</t>
+          <t>90709210755.5322</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>95256.379</t>
+          <t>95256378892.9291</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>99118.436</t>
+          <t>99118435730.2908</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>101736.902</t>
+          <t>101736902487.975</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>104769.475</t>
+          <t>104769474902.16</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>107607.103</t>
+          <t>107607102793.772</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>109637.748</t>
+          <t>109637748384.158</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>110990.959</t>
+          <t>110990959084.762</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>114289.628</t>
+          <t>114289627909.878</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>120922.406</t>
+          <t>120922405644.095</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>126214.668</t>
+          <t>126214667540.514</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>126450.741</t>
+          <t>126450741211.991</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>127513.784</t>
+          <t>127513784393.29</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>137380.623</t>
+          <t>137380623420.613</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>134949.702</t>
+          <t>134949701539.615</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>249.185</t>
+          <t>249184854.029122</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>248.52</t>
+          <t>248519519.971902</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>241.857</t>
+          <t>241856774.998349</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>237.705</t>
+          <t>237705284.919047</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>242.081</t>
+          <t>242080884.916954</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>246.374</t>
+          <t>246373744.267785</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>214.902</t>
+          <t>214902348.644951</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>252.273</t>
+          <t>252272807.837386</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>246.31</t>
+          <t>246309543.213824</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>264.975</t>
+          <t>264975153.276005</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>259.24</t>
+          <t>259240050.839006</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>262.318</t>
+          <t>262317634.354752</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>260.746</t>
+          <t>260746495.728625</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>258.964</t>
+          <t>258964094.34228</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>264.752</t>
+          <t>264751853.916203</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>12975.201</t>
+          <t>12975200697.3693</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13361.008</t>
+          <t>13361008438.6252</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13868.264</t>
+          <t>13868264336.7741</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14116.319</t>
+          <t>14116318573.6833</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14841.674</t>
+          <t>14841674257.3369</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>14271.112</t>
+          <t>14271111896.1009</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>14650.507</t>
+          <t>14650507326.0781</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>15175.783</t>
+          <t>15175782643.1129</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>15794.175</t>
+          <t>15794175122.5004</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>16254.97</t>
+          <t>16254969708.749</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16264.398</t>
+          <t>16264397928.3115</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>16401.095</t>
+          <t>16401094875.2895</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>16649.751</t>
+          <t>16649751480.1568</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>17040.491</t>
+          <t>17040491141.0682</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>17059.415</t>
+          <t>17059415297.4057</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>51610.874</t>
+          <t>51610873733.2739</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>52218.449</t>
+          <t>52218448574.3795</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>52626.032</t>
+          <t>52626031885.5784</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>52590.512</t>
+          <t>52590511955.8403</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>50914.569</t>
+          <t>50914569387.5399</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>49672.949</t>
+          <t>49672948586.3702</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>45122.535</t>
+          <t>45122535111.1273</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>43748.203</t>
+          <t>43748202947.5566</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>44483.476</t>
+          <t>44483476296.7141</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>45617.726</t>
+          <t>45617726490.6036</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>46964.328</t>
+          <t>46964328063.2213</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>48610.237</t>
+          <t>48610236641.668</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>49914.122</t>
+          <t>49914121522.7158</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>52177.421</t>
+          <t>52177420533.9095</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>51789.183</t>
+          <t>51789183356.9374</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7735.352</t>
+          <t>7735352006.76222</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7752.8</t>
+          <t>7752800148.63311</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>7587.843</t>
+          <t>7587843234.08424</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>7479.105</t>
+          <t>7479104590.68156</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7664.202</t>
+          <t>7664201899.18534</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7892.942</t>
+          <t>7892941676.58962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7971.467</t>
+          <t>7971466947.08877</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>7982.406</t>
+          <t>7982405698.00927</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>7973.38</t>
+          <t>7973380082.29008</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8280.831</t>
+          <t>8280830516.33083</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>8239.377</t>
+          <t>8239376660.20443</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>8574.075</t>
+          <t>8574074762.65842</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>8682.13</t>
+          <t>8682130106.79437</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>8759.392</t>
+          <t>8759391957.8558</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>8763.289</t>
+          <t>8763289000.42708</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20304.821</t>
+          <t>20304821187.2301</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20519.934</t>
+          <t>20519933585.6949</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18973.399</t>
+          <t>18973398779.476</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>18030.072</t>
+          <t>18030072074.4258</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21160.448</t>
+          <t>21160447799.65</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>20892.395</t>
+          <t>20892395357.6034</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20801.289</t>
+          <t>20801288548.5596</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>19260.344</t>
+          <t>19260344307.8519</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19455.049</t>
+          <t>19455049431.1378</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>19099.452</t>
+          <t>19099451821.5226</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19068.369</t>
+          <t>19068369497.6879</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>19337.341</t>
+          <t>19337341318.4837</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>19529.523</t>
+          <t>19529523096.7995</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>19989.05</t>
+          <t>19989049972.824</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>20021.904</t>
+          <t>20021904493.8034</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>297648.527</t>
+          <t>297648527323.495</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>289959.156</t>
+          <t>289959155807.974</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>277181.476</t>
+          <t>277181475849.671</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>263759.528</t>
+          <t>263759527817.316</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>265189.543</t>
+          <t>265189542990.295</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>269013.762</t>
+          <t>269013761684.971</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>270158.302</t>
+          <t>270158301710.431</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>271177.161</t>
+          <t>271177161045.45</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>272611.517</t>
+          <t>272611516779.597</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>274270.524</t>
+          <t>274270523999.906</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>274031.565</t>
+          <t>274031565165.403</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>274501.228</t>
+          <t>274501227837.341</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>276220.39</t>
+          <t>276220389625.392</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>275656.283</t>
+          <t>275656282978.686</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>266813.037</t>
+          <t>266813037195.971</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>7225.093</t>
+          <t>7225092859.21636</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6987.543</t>
+          <t>6987543336.50031</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6892.569</t>
+          <t>6892568532.40042</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>6686.814</t>
+          <t>6686813696.78546</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6417.546</t>
+          <t>6417546282.85426</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6272.017</t>
+          <t>6272016681.01793</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6230.878</t>
+          <t>6230878169.93828</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>5942.768</t>
+          <t>5942767540.74077</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>5810.972</t>
+          <t>5810972378.55502</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>6023.22</t>
+          <t>6023219861.86919</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>6096.426</t>
+          <t>6096425667.30265</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6043.446</t>
+          <t>6043446390.41681</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>6225.605</t>
+          <t>6225605153.08768</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>6510.983</t>
+          <t>6510983399.34685</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>6315.301</t>
+          <t>6315300694.58071</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2894.495</t>
+          <t>2894494820.17884</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2795.255</t>
+          <t>2795255127.12261</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2747.516</t>
+          <t>2747515730.22485</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2720.315</t>
+          <t>2720314532.4651</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2763.754</t>
+          <t>2763754279.91321</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2840.94</t>
+          <t>2840939978.8208</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2729.018</t>
+          <t>2729018362.71325</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2762.486</t>
+          <t>2762486038.17472</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2822.086</t>
+          <t>2822085698.2035</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2868.358</t>
+          <t>2868357956.55474</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2891.623</t>
+          <t>2891623125.51499</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2942.705</t>
+          <t>2942705186.31641</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>3010.003</t>
+          <t>3010003102.76135</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>3195.495</t>
+          <t>3195494548.21917</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>3142.705</t>
+          <t>3142704529.39801</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>11025.979</t>
+          <t>11025979213.882</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>11040.616</t>
+          <t>11040615546.1821</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10997.136</t>
+          <t>10997136155.1131</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>11173.333</t>
+          <t>11173332982.8887</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11536.087</t>
+          <t>11536086975.6413</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>12372.004</t>
+          <t>12372003621.3757</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>12660.641</t>
+          <t>12660641005.6478</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>12689.678</t>
+          <t>12689677605.8141</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>12604.081</t>
+          <t>12604080762.7359</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>12834.121</t>
+          <t>12834120574.7581</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>12955.645</t>
+          <t>12955644559.5042</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>13107.308</t>
+          <t>13107307855.991</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>13619.596</t>
+          <t>13619596402.0266</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>13935.954</t>
+          <t>13935954000.255</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>13472.292</t>
+          <t>13472291599.2382</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>42290.027</t>
+          <t>42290027358.7397</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>44724.599</t>
+          <t>44724599237.9609</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>45543.165</t>
+          <t>45543165415.3577</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>44236.114</t>
+          <t>44236114014.8563</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>44204.924</t>
+          <t>44204923535.5193</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>42106.389</t>
+          <t>42106389477.5405</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>42374.662</t>
+          <t>42374662069.43</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>42318.657</t>
+          <t>42318657240.0706</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>42622.763</t>
+          <t>42622762534.2492</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>42589.201</t>
+          <t>42589201002.5229</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>44786.053</t>
+          <t>44786053117.9557</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>43941.081</t>
+          <t>43941080725.7726</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>42903.882</t>
+          <t>42903882048.3703</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>44268.897</t>
+          <t>44268897433.4793</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>43515.056</t>
+          <t>43515056284.2318</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>26681.86</t>
+          <t>26681859651.1454</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>27010.109</t>
+          <t>27010108944.6499</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28269.098</t>
+          <t>28269097527.0605</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28735.476</t>
+          <t>28735475930.6147</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>29379.005</t>
+          <t>29379005457.9867</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>30450.132</t>
+          <t>30450131948.9993</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>29107.883</t>
+          <t>29107883425.9558</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>29814.808</t>
+          <t>29814808281.2706</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30579.781</t>
+          <t>30579780599.5971</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>31796.786</t>
+          <t>31796785650.6211</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>33016.744</t>
+          <t>33016744115.4356</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>33820.463</t>
+          <t>33820463318.1543</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>35090.558</t>
+          <t>35090557873.4356</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>36029.337</t>
+          <t>36029336500.4371</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>35551.296</t>
+          <t>35551295753.41</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>298161.937</t>
+          <t>298161937232.312</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>302919.672</t>
+          <t>302919672135.171</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>309080.234</t>
+          <t>309080234079.365</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>319415.158</t>
+          <t>319415158408.207</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>322325.414</t>
+          <t>322325413947.204</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>330311.496</t>
+          <t>330311496118.307</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>326768.833</t>
+          <t>326768833063.63</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>321250.719</t>
+          <t>321250718930.193</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>317376.456</t>
+          <t>317376455817.311</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>326060.577</t>
+          <t>326060577365.376</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>329582.565</t>
+          <t>329582565444.648</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>339062.65</t>
+          <t>339062649832.87</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>342265.886</t>
+          <t>342265886079.758</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>338919.521</t>
+          <t>338919521350.222</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>324371.408</t>
+          <t>324371408038.222</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2699948.91</t>
+          <t>2699948910191.81</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2791307.87</t>
+          <t>2791307870267.64</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2869241.928</t>
+          <t>2869241927547.02</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2921245.552</t>
+          <t>2921245551860.68</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2982579.389</t>
+          <t>2982579389049.23</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3155493.385</t>
+          <t>3155493384624.27</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3304607.713</t>
+          <t>3304607712821.75</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3437206.575</t>
+          <t>3437206574861.71</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>3628209.92</t>
+          <t>3628209920408.7</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>3824510.969</t>
+          <t>3824510969299.98</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>3930544.918</t>
+          <t>3930544918160.48</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>4108929.746</t>
+          <t>4108929746158.27</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>4220130.531</t>
+          <t>4220130531035.84</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>4431296.103</t>
+          <t>4431296102744.71</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>4564262.236</t>
+          <t>4564262236214.11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6892593.176</t>
+          <t>6892593175962.05</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7065663.187</t>
+          <t>7065663186694.99</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7192711.182</t>
+          <t>7192711182033.72</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7269378.67</t>
+          <t>7269378670237.37</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>7385203.603</t>
+          <t>7385203603434.81</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7693319.45</t>
+          <t>7693319449984.54</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7945250.166</t>
+          <t>7945250166345.18</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8127108.809</t>
+          <t>8127108808534.68</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8468085.877</t>
+          <t>8468085876564.43</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8808176.354</t>
+          <t>8808176354371.52</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>8999724.686</t>
+          <t>8999724685725.04</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>9300699.611</t>
+          <t>9300699611373.29</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>9450913.673</t>
+          <t>9450913673174.63</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>9780263.088</t>
+          <t>9780263088274.59</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>9896808.776</t>
+          <t>9896808775656.83</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
